--- a/deliverables/Onyx_2026_Medical_Plans_ADP_TriNet_Angle.xlsx
+++ b/deliverables/Onyx_2026_Medical_Plans_ADP_TriNet_Angle.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2038" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="243">
   <si>
     <t xml:space="preserve">Onyx Accounting Group, LLC - 2026 Medical Plan Comparison</t>
   </si>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Aetna ACO 6500 AZ</t>
   </si>
   <si>
-    <t xml:space="preserve">DERIVED, not stated.  70% of the cheapest Aetna plan's employee-only rate; reproduces TriNet's own published employee contributions to the penny on both carriers.  STILL NEEDED IN WRITING.</t>
+    <t xml:space="preserve">CONFIRMED by TriNet: 70% of the minimum funding on the lowest-cost plan offered.  Our derivation was right and reconciles to the penny on both carriers quoted.  Keyed to the ACO 6500's $385 employee-only rate.</t>
   </si>
   <si>
     <t xml:space="preserve">Angle</t>
@@ -276,7 +276,13 @@
     <t xml:space="preserve">5.  OPEN ITEMS THAT COULD MOVE THESE NUMBERS</t>
   </si>
   <si>
-    <t xml:space="preserve">•  TriNet's 70% contribution floor is derived, not documented.  Requested in writing.</t>
+    <t xml:space="preserve">•  TriNet says TWELVE plans are available; the strategy appendix we were given lists the SIXTEEN Aetna rungs in this workbook.  Which four are unavailable is unknown, so all sixteen are kept here.  It matters only if the ACO 6500 is not among the twelve - the $269.50 floor is keyed to its $385 rate, and dropping the four cheapest would push the floor to $364.00, above the $300 employee-only target.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  TriNet has confirmed its service fee is the $1,200/month minimum ($14,400/yr), its workers' compensation is $300, basic life at $10,000 is $67, and nothing else is required - no dental, no vision, and long-term disability is optional.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  TriNet allows different funding tiers by class, so Onyx could fund Steven at 100% while holding others at the fixed dollars.  Not modeled here - this workbook applies the stated tier targets uniformly.</t>
   </si>
   <si>
     <t xml:space="preserve">•  Whether Steven enrolls.  Family coverage for him is roughly $12,000/yr of Onyx contribution.</t>
@@ -1432,7 +1438,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1948,6 +1954,16 @@
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
         <v>86</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="6" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1985,17 +2001,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="O3" s="24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P3" s="24"/>
       <c r="Q3" s="24"/>
@@ -2006,43 +2022,43 @@
         <v>26</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="O4" s="10" t="s">
         <v>13</v>
@@ -2062,16 +2078,16 @@
         <v>32</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F5" s="20" t="n">
         <v>2000</v>
@@ -2089,16 +2105,16 @@
         <v>1</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M5" s="12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="N5" s="12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="O5" s="27" t="n">
         <v>640.66</v>
@@ -2118,16 +2134,16 @@
         <v>32</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F6" s="30" t="n">
         <v>2500</v>
@@ -2145,16 +2161,16 @@
         <v>1</v>
       </c>
       <c r="K6" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L6" s="28" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M6" s="28" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="N6" s="28" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="O6" s="32" t="n">
         <v>606.87</v>
@@ -2174,16 +2190,16 @@
         <v>32</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F7" s="20" t="n">
         <v>500</v>
@@ -2201,16 +2217,16 @@
         <v>0.8</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="O7" s="27" t="n">
         <v>882.91</v>
@@ -2230,16 +2246,16 @@
         <v>32</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F8" s="30" t="n">
         <v>1000</v>
@@ -2257,16 +2273,16 @@
         <v>0.8</v>
       </c>
       <c r="K8" s="28" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L8" s="28" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="M8" s="28" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N8" s="28" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="O8" s="32" t="n">
         <v>768.21</v>
@@ -2286,16 +2302,16 @@
         <v>32</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F9" s="20" t="n">
         <v>3500</v>
@@ -2313,16 +2329,16 @@
         <v>0.8</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="M9" s="12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="N9" s="12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="O9" s="27" t="n">
         <v>490.12</v>
@@ -2342,16 +2358,16 @@
         <v>32</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F10" s="30" t="n">
         <v>500</v>
@@ -2369,16 +2385,16 @@
         <v>0.8</v>
       </c>
       <c r="K10" s="28" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L10" s="28" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="M10" s="28" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N10" s="28" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="O10" s="32" t="n">
         <v>825.23</v>
@@ -2398,16 +2414,16 @@
         <v>32</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F11" s="20" t="n">
         <v>1000</v>
@@ -2425,16 +2441,16 @@
         <v>0.8</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="M11" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N11" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="O11" s="27" t="n">
         <v>749.15</v>
@@ -2454,16 +2470,16 @@
         <v>32</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E12" s="29" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F12" s="30" t="n">
         <v>1500</v>
@@ -2481,16 +2497,16 @@
         <v>1</v>
       </c>
       <c r="K12" s="28" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L12" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M12" s="28" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N12" s="28" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="O12" s="32" t="n">
         <v>744.88</v>
@@ -2510,16 +2526,16 @@
         <v>32</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F13" s="20" t="n">
         <v>6000</v>
@@ -2537,16 +2553,16 @@
         <v>0.8</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="M13" s="12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="O13" s="27" t="n">
         <v>437.9</v>
@@ -2566,16 +2582,16 @@
         <v>32</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F14" s="30" t="n">
         <v>3000</v>
@@ -2593,16 +2609,16 @@
         <v>0.8</v>
       </c>
       <c r="K14" s="28" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L14" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M14" s="28" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N14" s="28" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="O14" s="32" t="n">
         <v>629.01</v>
@@ -2625,13 +2641,13 @@
         <v>33</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F15" s="20" t="n">
         <v>8000</v>
@@ -2649,16 +2665,16 @@
         <v>0.8</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M15" s="12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="N15" s="12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="O15" s="27" t="n">
         <v>374.03</v>
@@ -2681,13 +2697,13 @@
         <v>36</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F16" s="30" t="n">
         <v>6500</v>
@@ -2705,16 +2721,16 @@
         <v>1</v>
       </c>
       <c r="K16" s="28" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L16" s="28" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="M16" s="28" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N16" s="28" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="O16" s="32" t="n">
         <v>385</v>
@@ -2734,16 +2750,16 @@
         <v>35</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F17" s="20" t="n">
         <v>7150</v>
@@ -2761,16 +2777,16 @@
         <v>1</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M17" s="12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N17" s="12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="O17" s="27" t="n">
         <v>400</v>
@@ -2790,16 +2806,16 @@
         <v>35</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F18" s="30" t="n">
         <v>6350</v>
@@ -2817,16 +2833,16 @@
         <v>1</v>
       </c>
       <c r="K18" s="28" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L18" s="28" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M18" s="28" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N18" s="28" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="O18" s="32" t="n">
         <v>410</v>
@@ -2846,16 +2862,16 @@
         <v>35</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F19" s="20" t="n">
         <v>4000</v>
@@ -2873,16 +2889,16 @@
         <v>0.8</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="M19" s="12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="O19" s="27" t="n">
         <v>494</v>
@@ -2902,16 +2918,16 @@
         <v>35</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D20" s="28" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F20" s="30" t="n">
         <v>2500</v>
@@ -2929,16 +2945,16 @@
         <v>0.8</v>
       </c>
       <c r="K20" s="28" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L20" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M20" s="28" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N20" s="28" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="O20" s="32" t="n">
         <v>520</v>
@@ -2958,16 +2974,16 @@
         <v>35</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F21" s="20" t="n">
         <v>5000</v>
@@ -2985,16 +3001,16 @@
         <v>0.7</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M21" s="12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O21" s="27" t="n">
         <v>530</v>
@@ -3014,16 +3030,16 @@
         <v>35</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E22" s="29" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F22" s="30" t="n">
         <v>2000</v>
@@ -3041,16 +3057,16 @@
         <v>0.7</v>
       </c>
       <c r="K22" s="28" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L22" s="28" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="M22" s="28" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N22" s="28" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="O22" s="32" t="n">
         <v>581</v>
@@ -3070,16 +3086,16 @@
         <v>35</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E23" s="25" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F23" s="20" t="n">
         <v>1000</v>
@@ -3097,16 +3113,16 @@
         <v>0.8</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="O23" s="27" t="n">
         <v>599</v>
@@ -3126,16 +3142,16 @@
         <v>35</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E24" s="29" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F24" s="30" t="n">
         <v>3000</v>
@@ -3153,16 +3169,16 @@
         <v>1</v>
       </c>
       <c r="K24" s="28" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L24" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M24" s="28" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N24" s="28" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="O24" s="32" t="n">
         <v>626</v>
@@ -3182,16 +3198,16 @@
         <v>35</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E25" s="25" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F25" s="20" t="n">
         <v>2000</v>
@@ -3209,16 +3225,16 @@
         <v>0.8</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M25" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N25" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="O25" s="27" t="n">
         <v>632</v>
@@ -3238,16 +3254,16 @@
         <v>35</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E26" s="29" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F26" s="30" t="n">
         <v>1000</v>
@@ -3265,16 +3281,16 @@
         <v>0.7</v>
       </c>
       <c r="K26" s="28" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L26" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M26" s="28" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N26" s="28" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="O26" s="32" t="n">
         <v>640</v>
@@ -3294,16 +3310,16 @@
         <v>35</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F27" s="20" t="n">
         <v>1000</v>
@@ -3321,16 +3337,16 @@
         <v>0.8</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="M27" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="O27" s="27" t="n">
         <v>670</v>
@@ -3350,16 +3366,16 @@
         <v>35</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E28" s="29" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F28" s="30" t="n">
         <v>2000</v>
@@ -3377,16 +3393,16 @@
         <v>1</v>
       </c>
       <c r="K28" s="28" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L28" s="28" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M28" s="28" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="N28" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O28" s="32" t="n">
         <v>590</v>
@@ -3406,16 +3422,16 @@
         <v>35</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F29" s="20" t="n">
         <v>750</v>
@@ -3433,16 +3449,16 @@
         <v>0.9</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="M29" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="O29" s="27" t="n">
         <v>743</v>
@@ -3462,16 +3478,16 @@
         <v>35</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D30" s="28" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E30" s="29" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F30" s="30" t="n">
         <v>0</v>
@@ -3489,16 +3505,16 @@
         <v>1</v>
       </c>
       <c r="K30" s="28" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L30" s="28" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="M30" s="28" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N30" s="28" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="O30" s="32" t="n">
         <v>794</v>
@@ -3518,16 +3534,16 @@
         <v>35</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E31" s="25" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F31" s="20" t="n">
         <v>300</v>
@@ -3545,16 +3561,16 @@
         <v>0.9</v>
       </c>
       <c r="K31" s="12" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="M31" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="O31" s="27" t="n">
         <v>863</v>
@@ -3577,13 +3593,13 @@
         <v>39</v>
       </c>
       <c r="C32" s="28" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D32" s="28" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E32" s="29" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F32" s="30" t="n">
         <v>3400</v>
@@ -3601,16 +3617,16 @@
         <v>0.8</v>
       </c>
       <c r="K32" s="28" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L32" s="28" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="M32" s="28" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="N32" s="28" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="O32" s="32" t="n">
         <v>439.03</v>
@@ -3630,16 +3646,16 @@
         <v>38</v>
       </c>
       <c r="B33" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D33" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="C33" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>195</v>
-      </c>
       <c r="E33" s="25" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F33" s="20" t="n">
         <v>2000</v>
@@ -3657,16 +3673,16 @@
         <v>0.8</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="M33" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N33" s="12" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="O33" s="27" t="n">
         <v>492.11</v>
@@ -3686,16 +3702,16 @@
         <v>38</v>
       </c>
       <c r="B34" s="28" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C34" s="28" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D34" s="28" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E34" s="29" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F34" s="30" t="n">
         <v>1000</v>
@@ -3713,16 +3729,16 @@
         <v>0.8</v>
       </c>
       <c r="K34" s="28" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L34" s="28" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M34" s="28" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N34" s="28" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O34" s="32" t="n">
         <v>546.33</v>
@@ -3739,12 +3755,12 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -3788,12 +3804,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3801,10 +3817,10 @@
         <v>26</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>7</v>
@@ -3813,16 +3829,16 @@
         <v>8</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="J4" s="10" t="s">
         <v>63</v>
@@ -3831,25 +3847,25 @@
         <v>65</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="O4" s="10" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="P4" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q4" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="R4" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3857,10 +3873,10 @@
         <v>32</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>12</v>
@@ -3926,10 +3942,10 @@
         <v>32</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D6" s="38" t="s">
         <v>15</v>
@@ -3995,10 +4011,10 @@
         <v>32</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>18</v>
@@ -4064,10 +4080,10 @@
         <v>32</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D8" s="38" t="s">
         <v>21</v>
@@ -4133,10 +4149,10 @@
         <v>32</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>12</v>
@@ -4202,10 +4218,10 @@
         <v>32</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D10" s="38" t="s">
         <v>15</v>
@@ -4271,10 +4287,10 @@
         <v>32</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>18</v>
@@ -4340,10 +4356,10 @@
         <v>32</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D12" s="38" t="s">
         <v>21</v>
@@ -4409,10 +4425,10 @@
         <v>32</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>12</v>
@@ -4478,10 +4494,10 @@
         <v>32</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D14" s="38" t="s">
         <v>15</v>
@@ -4547,10 +4563,10 @@
         <v>32</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>18</v>
@@ -4616,10 +4632,10 @@
         <v>32</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D16" s="38" t="s">
         <v>21</v>
@@ -4685,10 +4701,10 @@
         <v>32</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>12</v>
@@ -4754,10 +4770,10 @@
         <v>32</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D18" s="38" t="s">
         <v>15</v>
@@ -4823,10 +4839,10 @@
         <v>32</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>18</v>
@@ -4892,10 +4908,10 @@
         <v>32</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D20" s="38" t="s">
         <v>21</v>
@@ -4961,10 +4977,10 @@
         <v>32</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>12</v>
@@ -5030,10 +5046,10 @@
         <v>32</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>15</v>
@@ -5099,10 +5115,10 @@
         <v>32</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>18</v>
@@ -5168,10 +5184,10 @@
         <v>32</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>21</v>
@@ -5237,10 +5253,10 @@
         <v>32</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>12</v>
@@ -5306,10 +5322,10 @@
         <v>32</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D26" s="38" t="s">
         <v>15</v>
@@ -5375,10 +5391,10 @@
         <v>32</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>18</v>
@@ -5444,10 +5460,10 @@
         <v>32</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D28" s="38" t="s">
         <v>21</v>
@@ -5513,10 +5529,10 @@
         <v>32</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>12</v>
@@ -5582,10 +5598,10 @@
         <v>32</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D30" s="38" t="s">
         <v>15</v>
@@ -5651,10 +5667,10 @@
         <v>32</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>18</v>
@@ -5720,10 +5736,10 @@
         <v>32</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D32" s="38" t="s">
         <v>21</v>
@@ -5789,10 +5805,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>12</v>
@@ -5858,10 +5874,10 @@
         <v>32</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D34" s="38" t="s">
         <v>15</v>
@@ -5927,10 +5943,10 @@
         <v>32</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>18</v>
@@ -5996,10 +6012,10 @@
         <v>32</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C36" s="38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D36" s="38" t="s">
         <v>21</v>
@@ -6065,10 +6081,10 @@
         <v>32</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D37" s="11" t="s">
         <v>12</v>
@@ -6134,10 +6150,10 @@
         <v>32</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D38" s="38" t="s">
         <v>15</v>
@@ -6203,10 +6219,10 @@
         <v>32</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>18</v>
@@ -6272,10 +6288,10 @@
         <v>32</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D40" s="38" t="s">
         <v>21</v>
@@ -6341,10 +6357,10 @@
         <v>32</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D41" s="11" t="s">
         <v>12</v>
@@ -6410,10 +6426,10 @@
         <v>32</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C42" s="38" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D42" s="38" t="s">
         <v>15</v>
@@ -6479,10 +6495,10 @@
         <v>32</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>18</v>
@@ -6548,10 +6564,10 @@
         <v>32</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C44" s="38" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D44" s="38" t="s">
         <v>21</v>
@@ -6620,7 +6636,7 @@
         <v>33</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D45" s="11" t="s">
         <v>12</v>
@@ -6689,7 +6705,7 @@
         <v>33</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D46" s="38" t="s">
         <v>15</v>
@@ -6758,7 +6774,7 @@
         <v>33</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D47" s="11" t="s">
         <v>18</v>
@@ -6827,7 +6843,7 @@
         <v>33</v>
       </c>
       <c r="C48" s="38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D48" s="38" t="s">
         <v>21</v>
@@ -6896,7 +6912,7 @@
         <v>36</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D49" s="11" t="s">
         <v>12</v>
@@ -6965,7 +6981,7 @@
         <v>36</v>
       </c>
       <c r="C50" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D50" s="38" t="s">
         <v>15</v>
@@ -7034,7 +7050,7 @@
         <v>36</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D51" s="11" t="s">
         <v>18</v>
@@ -7103,7 +7119,7 @@
         <v>36</v>
       </c>
       <c r="C52" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D52" s="38" t="s">
         <v>21</v>
@@ -7169,10 +7185,10 @@
         <v>35</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D53" s="11" t="s">
         <v>12</v>
@@ -7238,10 +7254,10 @@
         <v>35</v>
       </c>
       <c r="B54" s="38" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C54" s="38" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D54" s="38" t="s">
         <v>15</v>
@@ -7307,10 +7323,10 @@
         <v>35</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D55" s="11" t="s">
         <v>18</v>
@@ -7376,10 +7392,10 @@
         <v>35</v>
       </c>
       <c r="B56" s="38" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C56" s="38" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D56" s="38" t="s">
         <v>21</v>
@@ -7445,10 +7461,10 @@
         <v>35</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D57" s="11" t="s">
         <v>12</v>
@@ -7514,10 +7530,10 @@
         <v>35</v>
       </c>
       <c r="B58" s="38" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C58" s="38" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D58" s="38" t="s">
         <v>15</v>
@@ -7583,10 +7599,10 @@
         <v>35</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D59" s="11" t="s">
         <v>18</v>
@@ -7652,10 +7668,10 @@
         <v>35</v>
       </c>
       <c r="B60" s="38" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C60" s="38" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D60" s="38" t="s">
         <v>21</v>
@@ -7721,10 +7737,10 @@
         <v>35</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D61" s="11" t="s">
         <v>12</v>
@@ -7790,10 +7806,10 @@
         <v>35</v>
       </c>
       <c r="B62" s="38" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C62" s="38" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D62" s="38" t="s">
         <v>15</v>
@@ -7859,10 +7875,10 @@
         <v>35</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D63" s="11" t="s">
         <v>18</v>
@@ -7928,10 +7944,10 @@
         <v>35</v>
       </c>
       <c r="B64" s="38" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C64" s="38" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D64" s="38" t="s">
         <v>21</v>
@@ -7997,10 +8013,10 @@
         <v>35</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D65" s="11" t="s">
         <v>12</v>
@@ -8066,10 +8082,10 @@
         <v>35</v>
       </c>
       <c r="B66" s="38" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C66" s="38" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D66" s="38" t="s">
         <v>15</v>
@@ -8135,10 +8151,10 @@
         <v>35</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D67" s="11" t="s">
         <v>18</v>
@@ -8204,10 +8220,10 @@
         <v>35</v>
       </c>
       <c r="B68" s="38" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C68" s="38" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D68" s="38" t="s">
         <v>21</v>
@@ -8273,10 +8289,10 @@
         <v>35</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D69" s="11" t="s">
         <v>12</v>
@@ -8342,10 +8358,10 @@
         <v>35</v>
       </c>
       <c r="B70" s="38" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C70" s="38" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D70" s="38" t="s">
         <v>15</v>
@@ -8411,10 +8427,10 @@
         <v>35</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D71" s="11" t="s">
         <v>18</v>
@@ -8480,10 +8496,10 @@
         <v>35</v>
       </c>
       <c r="B72" s="38" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C72" s="38" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D72" s="38" t="s">
         <v>21</v>
@@ -8549,10 +8565,10 @@
         <v>35</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D73" s="11" t="s">
         <v>12</v>
@@ -8618,10 +8634,10 @@
         <v>35</v>
       </c>
       <c r="B74" s="38" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C74" s="38" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D74" s="38" t="s">
         <v>15</v>
@@ -8687,10 +8703,10 @@
         <v>35</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D75" s="11" t="s">
         <v>18</v>
@@ -8756,10 +8772,10 @@
         <v>35</v>
       </c>
       <c r="B76" s="38" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C76" s="38" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D76" s="38" t="s">
         <v>21</v>
@@ -8825,10 +8841,10 @@
         <v>35</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D77" s="11" t="s">
         <v>12</v>
@@ -8894,10 +8910,10 @@
         <v>35</v>
       </c>
       <c r="B78" s="38" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C78" s="38" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D78" s="38" t="s">
         <v>15</v>
@@ -8963,10 +8979,10 @@
         <v>35</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D79" s="11" t="s">
         <v>18</v>
@@ -9032,10 +9048,10 @@
         <v>35</v>
       </c>
       <c r="B80" s="38" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C80" s="38" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D80" s="38" t="s">
         <v>21</v>
@@ -9101,10 +9117,10 @@
         <v>35</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D81" s="11" t="s">
         <v>12</v>
@@ -9170,10 +9186,10 @@
         <v>35</v>
       </c>
       <c r="B82" s="38" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C82" s="38" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D82" s="38" t="s">
         <v>15</v>
@@ -9239,10 +9255,10 @@
         <v>35</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D83" s="11" t="s">
         <v>18</v>
@@ -9308,10 +9324,10 @@
         <v>35</v>
       </c>
       <c r="B84" s="38" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C84" s="38" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D84" s="38" t="s">
         <v>21</v>
@@ -9377,10 +9393,10 @@
         <v>35</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D85" s="11" t="s">
         <v>12</v>
@@ -9446,10 +9462,10 @@
         <v>35</v>
       </c>
       <c r="B86" s="38" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C86" s="38" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D86" s="38" t="s">
         <v>15</v>
@@ -9515,10 +9531,10 @@
         <v>35</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D87" s="11" t="s">
         <v>18</v>
@@ -9584,10 +9600,10 @@
         <v>35</v>
       </c>
       <c r="B88" s="38" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C88" s="38" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D88" s="38" t="s">
         <v>21</v>
@@ -9653,10 +9669,10 @@
         <v>35</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D89" s="11" t="s">
         <v>12</v>
@@ -9722,10 +9738,10 @@
         <v>35</v>
       </c>
       <c r="B90" s="38" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C90" s="38" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D90" s="38" t="s">
         <v>15</v>
@@ -9791,10 +9807,10 @@
         <v>35</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D91" s="11" t="s">
         <v>18</v>
@@ -9860,10 +9876,10 @@
         <v>35</v>
       </c>
       <c r="B92" s="38" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C92" s="38" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D92" s="38" t="s">
         <v>21</v>
@@ -9929,10 +9945,10 @@
         <v>35</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D93" s="11" t="s">
         <v>12</v>
@@ -9998,10 +10014,10 @@
         <v>35</v>
       </c>
       <c r="B94" s="38" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C94" s="38" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D94" s="38" t="s">
         <v>15</v>
@@ -10067,10 +10083,10 @@
         <v>35</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D95" s="11" t="s">
         <v>18</v>
@@ -10136,10 +10152,10 @@
         <v>35</v>
       </c>
       <c r="B96" s="38" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C96" s="38" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D96" s="38" t="s">
         <v>21</v>
@@ -10205,10 +10221,10 @@
         <v>35</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D97" s="11" t="s">
         <v>12</v>
@@ -10274,10 +10290,10 @@
         <v>35</v>
       </c>
       <c r="B98" s="38" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C98" s="38" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D98" s="38" t="s">
         <v>15</v>
@@ -10343,10 +10359,10 @@
         <v>35</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D99" s="11" t="s">
         <v>18</v>
@@ -10412,10 +10428,10 @@
         <v>35</v>
       </c>
       <c r="B100" s="38" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C100" s="38" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D100" s="38" t="s">
         <v>21</v>
@@ -10481,10 +10497,10 @@
         <v>35</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D101" s="11" t="s">
         <v>12</v>
@@ -10550,10 +10566,10 @@
         <v>35</v>
       </c>
       <c r="B102" s="38" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C102" s="38" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D102" s="38" t="s">
         <v>15</v>
@@ -10619,10 +10635,10 @@
         <v>35</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D103" s="11" t="s">
         <v>18</v>
@@ -10688,10 +10704,10 @@
         <v>35</v>
       </c>
       <c r="B104" s="38" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C104" s="38" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D104" s="38" t="s">
         <v>21</v>
@@ -10757,10 +10773,10 @@
         <v>35</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D105" s="11" t="s">
         <v>12</v>
@@ -10826,10 +10842,10 @@
         <v>35</v>
       </c>
       <c r="B106" s="38" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C106" s="38" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D106" s="38" t="s">
         <v>15</v>
@@ -10895,10 +10911,10 @@
         <v>35</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D107" s="11" t="s">
         <v>18</v>
@@ -10964,10 +10980,10 @@
         <v>35</v>
       </c>
       <c r="B108" s="38" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C108" s="38" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D108" s="38" t="s">
         <v>21</v>
@@ -11033,10 +11049,10 @@
         <v>35</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D109" s="11" t="s">
         <v>12</v>
@@ -11102,10 +11118,10 @@
         <v>35</v>
       </c>
       <c r="B110" s="38" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C110" s="38" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D110" s="38" t="s">
         <v>15</v>
@@ -11171,10 +11187,10 @@
         <v>35</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D111" s="11" t="s">
         <v>18</v>
@@ -11240,10 +11256,10 @@
         <v>35</v>
       </c>
       <c r="B112" s="38" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C112" s="38" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D112" s="38" t="s">
         <v>21</v>
@@ -11312,7 +11328,7 @@
         <v>39</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D113" s="11" t="s">
         <v>12</v>
@@ -11381,7 +11397,7 @@
         <v>39</v>
       </c>
       <c r="C114" s="38" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D114" s="38" t="s">
         <v>15</v>
@@ -11450,7 +11466,7 @@
         <v>39</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D115" s="11" t="s">
         <v>18</v>
@@ -11519,7 +11535,7 @@
         <v>39</v>
       </c>
       <c r="C116" s="38" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D116" s="38" t="s">
         <v>21</v>
@@ -11585,10 +11601,10 @@
         <v>38</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D117" s="11" t="s">
         <v>12</v>
@@ -11654,10 +11670,10 @@
         <v>38</v>
       </c>
       <c r="B118" s="38" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C118" s="38" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D118" s="38" t="s">
         <v>15</v>
@@ -11723,10 +11739,10 @@
         <v>38</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D119" s="11" t="s">
         <v>18</v>
@@ -11792,10 +11808,10 @@
         <v>38</v>
       </c>
       <c r="B120" s="38" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C120" s="38" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D120" s="38" t="s">
         <v>21</v>
@@ -11861,10 +11877,10 @@
         <v>38</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D121" s="11" t="s">
         <v>12</v>
@@ -11930,10 +11946,10 @@
         <v>38</v>
       </c>
       <c r="B122" s="38" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C122" s="38" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D122" s="38" t="s">
         <v>15</v>
@@ -11999,10 +12015,10 @@
         <v>38</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D123" s="11" t="s">
         <v>18</v>
@@ -12068,10 +12084,10 @@
         <v>38</v>
       </c>
       <c r="B124" s="38" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C124" s="38" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D124" s="38" t="s">
         <v>21</v>
@@ -12134,12 +12150,12 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -12175,12 +12191,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12188,34 +12204,34 @@
         <v>26</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12223,10 +12239,10 @@
         <v>32</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D5" s="33" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C5,'Plan Design'!$C$5:$C$34,0))</f>
@@ -12266,10 +12282,10 @@
         <v>32</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D6" s="39" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C6,'Plan Design'!$C$5:$C$34,0))</f>
@@ -12309,10 +12325,10 @@
         <v>32</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D7" s="33" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C7,'Plan Design'!$C$5:$C$34,0))</f>
@@ -12352,10 +12368,10 @@
         <v>32</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D8" s="39" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C8,'Plan Design'!$C$5:$C$34,0))</f>
@@ -12395,10 +12411,10 @@
         <v>32</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D9" s="33" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C9,'Plan Design'!$C$5:$C$34,0))</f>
@@ -12438,10 +12454,10 @@
         <v>32</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D10" s="39" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C10,'Plan Design'!$C$5:$C$34,0))</f>
@@ -12481,10 +12497,10 @@
         <v>32</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D11" s="33" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C11,'Plan Design'!$C$5:$C$34,0))</f>
@@ -12524,10 +12540,10 @@
         <v>32</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D12" s="39" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C12,'Plan Design'!$C$5:$C$34,0))</f>
@@ -12567,10 +12583,10 @@
         <v>32</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D13" s="33" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C13,'Plan Design'!$C$5:$C$34,0))</f>
@@ -12610,10 +12626,10 @@
         <v>32</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D14" s="39" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C14,'Plan Design'!$C$5:$C$34,0))</f>
@@ -12656,7 +12672,7 @@
         <v>33</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D15" s="33" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C15,'Plan Design'!$C$5:$C$34,0))</f>
@@ -12699,7 +12715,7 @@
         <v>36</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D16" s="39" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C16,'Plan Design'!$C$5:$C$34,0))</f>
@@ -12739,10 +12755,10 @@
         <v>35</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D17" s="33" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C17,'Plan Design'!$C$5:$C$34,0))</f>
@@ -12782,10 +12798,10 @@
         <v>35</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D18" s="39" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C18,'Plan Design'!$C$5:$C$34,0))</f>
@@ -12825,10 +12841,10 @@
         <v>35</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D19" s="33" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C19,'Plan Design'!$C$5:$C$34,0))</f>
@@ -12868,10 +12884,10 @@
         <v>35</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D20" s="39" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C20,'Plan Design'!$C$5:$C$34,0))</f>
@@ -12911,10 +12927,10 @@
         <v>35</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D21" s="33" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C21,'Plan Design'!$C$5:$C$34,0))</f>
@@ -12954,10 +12970,10 @@
         <v>35</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D22" s="39" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C22,'Plan Design'!$C$5:$C$34,0))</f>
@@ -12997,10 +13013,10 @@
         <v>35</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D23" s="33" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C23,'Plan Design'!$C$5:$C$34,0))</f>
@@ -13040,10 +13056,10 @@
         <v>35</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D24" s="39" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C24,'Plan Design'!$C$5:$C$34,0))</f>
@@ -13083,10 +13099,10 @@
         <v>35</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D25" s="33" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C25,'Plan Design'!$C$5:$C$34,0))</f>
@@ -13126,10 +13142,10 @@
         <v>35</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D26" s="39" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C26,'Plan Design'!$C$5:$C$34,0))</f>
@@ -13169,10 +13185,10 @@
         <v>35</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D27" s="33" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C27,'Plan Design'!$C$5:$C$34,0))</f>
@@ -13212,10 +13228,10 @@
         <v>35</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D28" s="39" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C28,'Plan Design'!$C$5:$C$34,0))</f>
@@ -13255,10 +13271,10 @@
         <v>35</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D29" s="33" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C29,'Plan Design'!$C$5:$C$34,0))</f>
@@ -13298,10 +13314,10 @@
         <v>35</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D30" s="39" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C30,'Plan Design'!$C$5:$C$34,0))</f>
@@ -13341,10 +13357,10 @@
         <v>35</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D31" s="33" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C31,'Plan Design'!$C$5:$C$34,0))</f>
@@ -13387,7 +13403,7 @@
         <v>39</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D32" s="39" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C32,'Plan Design'!$C$5:$C$34,0))</f>
@@ -13427,10 +13443,10 @@
         <v>38</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D33" s="33" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C33,'Plan Design'!$C$5:$C$34,0))</f>
@@ -13470,10 +13486,10 @@
         <v>38</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D34" s="39" t="str">
         <f aca="false">INDEX('Plan Design'!$E$5:$E$34,MATCH($C34,'Plan Design'!$C$5:$C$34,0))</f>
@@ -13510,12 +13526,12 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -13553,12 +13569,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13575,34 +13591,34 @@
         <v>26</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13619,10 +13635,10 @@
         <v>32</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G5" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F5&amp;"|"&amp;$C5,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -13671,10 +13687,10 @@
         <v>32</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G6" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F6&amp;"|"&amp;$C6,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -13723,10 +13739,10 @@
         <v>32</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G7" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F7&amp;"|"&amp;$C7,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -13775,10 +13791,10 @@
         <v>32</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G8" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F8&amp;"|"&amp;$C8,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -13827,10 +13843,10 @@
         <v>32</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G9" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F9&amp;"|"&amp;$C9,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -13879,10 +13895,10 @@
         <v>32</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G10" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F10&amp;"|"&amp;$C10,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -13931,10 +13947,10 @@
         <v>32</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G11" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F11&amp;"|"&amp;$C11,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -13983,10 +13999,10 @@
         <v>32</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G12" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F12&amp;"|"&amp;$C12,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -14035,10 +14051,10 @@
         <v>32</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G13" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F13&amp;"|"&amp;$C13,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -14087,10 +14103,10 @@
         <v>32</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G14" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F14&amp;"|"&amp;$C14,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -14142,7 +14158,7 @@
         <v>33</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G15" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F15&amp;"|"&amp;$C15,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -14194,7 +14210,7 @@
         <v>36</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G16" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F16&amp;"|"&amp;$C16,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -14243,10 +14259,10 @@
         <v>35</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G17" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F17&amp;"|"&amp;$C17,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -14295,10 +14311,10 @@
         <v>35</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G18" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F18&amp;"|"&amp;$C18,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -14347,10 +14363,10 @@
         <v>35</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G19" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F19&amp;"|"&amp;$C19,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -14399,10 +14415,10 @@
         <v>35</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G20" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F20&amp;"|"&amp;$C20,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -14451,10 +14467,10 @@
         <v>35</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G21" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F21&amp;"|"&amp;$C21,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -14503,10 +14519,10 @@
         <v>35</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G22" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F22&amp;"|"&amp;$C22,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -14555,10 +14571,10 @@
         <v>35</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G23" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F23&amp;"|"&amp;$C23,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -14607,10 +14623,10 @@
         <v>35</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G24" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F24&amp;"|"&amp;$C24,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -14659,10 +14675,10 @@
         <v>35</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G25" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F25&amp;"|"&amp;$C25,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -14711,10 +14727,10 @@
         <v>35</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G26" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F26&amp;"|"&amp;$C26,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -14763,10 +14779,10 @@
         <v>35</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G27" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F27&amp;"|"&amp;$C27,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -14815,10 +14831,10 @@
         <v>35</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G28" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F28&amp;"|"&amp;$C28,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -14867,10 +14883,10 @@
         <v>35</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G29" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F29&amp;"|"&amp;$C29,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -14919,10 +14935,10 @@
         <v>35</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G30" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F30&amp;"|"&amp;$C30,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -14971,10 +14987,10 @@
         <v>35</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G31" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F31&amp;"|"&amp;$C31,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -15026,7 +15042,7 @@
         <v>39</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G32" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F32&amp;"|"&amp;$C32,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -15075,10 +15091,10 @@
         <v>38</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G33" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F33&amp;"|"&amp;$C33,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -15127,10 +15143,10 @@
         <v>38</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G34" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F34&amp;"|"&amp;$C34,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -15179,10 +15195,10 @@
         <v>32</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G35" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F35&amp;"|"&amp;$C35,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -15231,10 +15247,10 @@
         <v>32</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G36" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F36&amp;"|"&amp;$C36,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -15283,10 +15299,10 @@
         <v>32</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G37" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F37&amp;"|"&amp;$C37,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -15335,10 +15351,10 @@
         <v>32</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G38" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F38&amp;"|"&amp;$C38,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -15387,10 +15403,10 @@
         <v>32</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G39" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F39&amp;"|"&amp;$C39,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -15439,10 +15455,10 @@
         <v>32</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G40" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F40&amp;"|"&amp;$C40,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -15491,10 +15507,10 @@
         <v>32</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G41" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F41&amp;"|"&amp;$C41,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -15543,10 +15559,10 @@
         <v>32</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G42" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F42&amp;"|"&amp;$C42,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -15595,10 +15611,10 @@
         <v>32</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G43" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F43&amp;"|"&amp;$C43,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -15647,10 +15663,10 @@
         <v>32</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G44" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F44&amp;"|"&amp;$C44,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -15702,7 +15718,7 @@
         <v>33</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G45" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F45&amp;"|"&amp;$C45,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -15754,7 +15770,7 @@
         <v>36</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G46" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F46&amp;"|"&amp;$C46,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -15803,10 +15819,10 @@
         <v>35</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G47" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F47&amp;"|"&amp;$C47,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -15855,10 +15871,10 @@
         <v>35</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G48" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F48&amp;"|"&amp;$C48,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -15907,10 +15923,10 @@
         <v>35</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G49" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F49&amp;"|"&amp;$C49,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -15959,10 +15975,10 @@
         <v>35</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G50" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F50&amp;"|"&amp;$C50,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -16011,10 +16027,10 @@
         <v>35</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G51" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F51&amp;"|"&amp;$C51,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -16063,10 +16079,10 @@
         <v>35</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G52" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F52&amp;"|"&amp;$C52,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -16115,10 +16131,10 @@
         <v>35</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G53" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F53&amp;"|"&amp;$C53,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -16167,10 +16183,10 @@
         <v>35</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G54" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F54&amp;"|"&amp;$C54,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -16219,10 +16235,10 @@
         <v>35</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G55" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F55&amp;"|"&amp;$C55,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -16271,10 +16287,10 @@
         <v>35</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G56" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F56&amp;"|"&amp;$C56,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -16323,10 +16339,10 @@
         <v>35</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G57" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F57&amp;"|"&amp;$C57,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -16375,10 +16391,10 @@
         <v>35</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G58" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F58&amp;"|"&amp;$C58,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -16427,10 +16443,10 @@
         <v>35</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G59" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F59&amp;"|"&amp;$C59,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -16479,10 +16495,10 @@
         <v>35</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G60" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F60&amp;"|"&amp;$C60,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -16531,10 +16547,10 @@
         <v>35</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G61" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F61&amp;"|"&amp;$C61,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -16586,7 +16602,7 @@
         <v>39</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G62" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F62&amp;"|"&amp;$C62,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -16635,10 +16651,10 @@
         <v>38</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G63" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F63&amp;"|"&amp;$C63,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -16687,10 +16703,10 @@
         <v>38</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G64" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F64&amp;"|"&amp;$C64,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -16739,10 +16755,10 @@
         <v>32</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G65" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F65&amp;"|"&amp;$C65,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -16791,10 +16807,10 @@
         <v>32</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G66" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F66&amp;"|"&amp;$C66,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -16843,10 +16859,10 @@
         <v>32</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G67" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F67&amp;"|"&amp;$C67,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -16895,10 +16911,10 @@
         <v>32</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G68" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F68&amp;"|"&amp;$C68,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -16947,10 +16963,10 @@
         <v>32</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G69" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F69&amp;"|"&amp;$C69,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -16999,10 +17015,10 @@
         <v>32</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G70" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F70&amp;"|"&amp;$C70,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -17051,10 +17067,10 @@
         <v>32</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G71" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F71&amp;"|"&amp;$C71,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -17103,10 +17119,10 @@
         <v>32</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G72" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F72&amp;"|"&amp;$C72,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -17155,10 +17171,10 @@
         <v>32</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G73" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F73&amp;"|"&amp;$C73,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -17207,10 +17223,10 @@
         <v>32</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G74" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F74&amp;"|"&amp;$C74,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -17262,7 +17278,7 @@
         <v>33</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G75" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F75&amp;"|"&amp;$C75,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -17314,7 +17330,7 @@
         <v>36</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G76" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F76&amp;"|"&amp;$C76,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -17363,10 +17379,10 @@
         <v>35</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G77" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F77&amp;"|"&amp;$C77,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -17415,10 +17431,10 @@
         <v>35</v>
       </c>
       <c r="E78" s="11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G78" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F78&amp;"|"&amp;$C78,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -17467,10 +17483,10 @@
         <v>35</v>
       </c>
       <c r="E79" s="11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G79" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F79&amp;"|"&amp;$C79,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -17519,10 +17535,10 @@
         <v>35</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G80" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F80&amp;"|"&amp;$C80,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -17571,10 +17587,10 @@
         <v>35</v>
       </c>
       <c r="E81" s="11" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G81" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F81&amp;"|"&amp;$C81,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -17623,10 +17639,10 @@
         <v>35</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G82" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F82&amp;"|"&amp;$C82,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -17675,10 +17691,10 @@
         <v>35</v>
       </c>
       <c r="E83" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G83" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F83&amp;"|"&amp;$C83,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -17727,10 +17743,10 @@
         <v>35</v>
       </c>
       <c r="E84" s="11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G84" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F84&amp;"|"&amp;$C84,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -17779,10 +17795,10 @@
         <v>35</v>
       </c>
       <c r="E85" s="11" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G85" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F85&amp;"|"&amp;$C85,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -17831,10 +17847,10 @@
         <v>35</v>
       </c>
       <c r="E86" s="11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G86" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F86&amp;"|"&amp;$C86,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -17883,10 +17899,10 @@
         <v>35</v>
       </c>
       <c r="E87" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F87" s="11" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G87" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F87&amp;"|"&amp;$C87,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -17935,10 +17951,10 @@
         <v>35</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F88" s="11" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G88" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F88&amp;"|"&amp;$C88,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -17987,10 +18003,10 @@
         <v>35</v>
       </c>
       <c r="E89" s="11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F89" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G89" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F89&amp;"|"&amp;$C89,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -18039,10 +18055,10 @@
         <v>35</v>
       </c>
       <c r="E90" s="11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G90" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F90&amp;"|"&amp;$C90,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -18091,10 +18107,10 @@
         <v>35</v>
       </c>
       <c r="E91" s="11" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F91" s="11" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G91" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F91&amp;"|"&amp;$C91,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -18146,7 +18162,7 @@
         <v>39</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G92" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F92&amp;"|"&amp;$C92,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -18195,10 +18211,10 @@
         <v>38</v>
       </c>
       <c r="E93" s="11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F93" s="11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G93" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F93&amp;"|"&amp;$C93,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -18247,10 +18263,10 @@
         <v>38</v>
       </c>
       <c r="E94" s="11" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G94" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F94&amp;"|"&amp;$C94,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -18299,10 +18315,10 @@
         <v>32</v>
       </c>
       <c r="E95" s="11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F95" s="11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G95" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F95&amp;"|"&amp;$C95,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -18351,10 +18367,10 @@
         <v>32</v>
       </c>
       <c r="E96" s="11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F96" s="11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G96" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F96&amp;"|"&amp;$C96,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -18403,10 +18419,10 @@
         <v>32</v>
       </c>
       <c r="E97" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F97" s="11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G97" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F97&amp;"|"&amp;$C97,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -18455,10 +18471,10 @@
         <v>32</v>
       </c>
       <c r="E98" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F98" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G98" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F98&amp;"|"&amp;$C98,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -18507,10 +18523,10 @@
         <v>32</v>
       </c>
       <c r="E99" s="11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F99" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G99" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F99&amp;"|"&amp;$C99,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -18559,10 +18575,10 @@
         <v>32</v>
       </c>
       <c r="E100" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F100" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G100" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F100&amp;"|"&amp;$C100,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -18611,10 +18627,10 @@
         <v>32</v>
       </c>
       <c r="E101" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G101" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F101&amp;"|"&amp;$C101,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -18663,10 +18679,10 @@
         <v>32</v>
       </c>
       <c r="E102" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F102" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G102" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F102&amp;"|"&amp;$C102,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -18715,10 +18731,10 @@
         <v>32</v>
       </c>
       <c r="E103" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F103" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G103" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F103&amp;"|"&amp;$C103,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -18767,10 +18783,10 @@
         <v>32</v>
       </c>
       <c r="E104" s="11" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F104" s="11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G104" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F104&amp;"|"&amp;$C104,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -18822,7 +18838,7 @@
         <v>33</v>
       </c>
       <c r="F105" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G105" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F105&amp;"|"&amp;$C105,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -18874,7 +18890,7 @@
         <v>36</v>
       </c>
       <c r="F106" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G106" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F106&amp;"|"&amp;$C106,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -18923,10 +18939,10 @@
         <v>35</v>
       </c>
       <c r="E107" s="11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F107" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G107" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F107&amp;"|"&amp;$C107,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -18975,10 +18991,10 @@
         <v>35</v>
       </c>
       <c r="E108" s="11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F108" s="11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G108" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F108&amp;"|"&amp;$C108,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -19027,10 +19043,10 @@
         <v>35</v>
       </c>
       <c r="E109" s="11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F109" s="11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G109" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F109&amp;"|"&amp;$C109,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -19079,10 +19095,10 @@
         <v>35</v>
       </c>
       <c r="E110" s="11" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F110" s="11" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G110" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F110&amp;"|"&amp;$C110,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -19131,10 +19147,10 @@
         <v>35</v>
       </c>
       <c r="E111" s="11" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F111" s="11" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G111" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F111&amp;"|"&amp;$C111,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -19183,10 +19199,10 @@
         <v>35</v>
       </c>
       <c r="E112" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F112" s="11" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G112" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F112&amp;"|"&amp;$C112,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -19235,10 +19251,10 @@
         <v>35</v>
       </c>
       <c r="E113" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F113" s="11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G113" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F113&amp;"|"&amp;$C113,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -19287,10 +19303,10 @@
         <v>35</v>
       </c>
       <c r="E114" s="11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G114" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F114&amp;"|"&amp;$C114,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -19339,10 +19355,10 @@
         <v>35</v>
       </c>
       <c r="E115" s="11" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F115" s="11" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G115" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F115&amp;"|"&amp;$C115,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -19391,10 +19407,10 @@
         <v>35</v>
       </c>
       <c r="E116" s="11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G116" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F116&amp;"|"&amp;$C116,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -19443,10 +19459,10 @@
         <v>35</v>
       </c>
       <c r="E117" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F117" s="11" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G117" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F117&amp;"|"&amp;$C117,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -19495,10 +19511,10 @@
         <v>35</v>
       </c>
       <c r="E118" s="11" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F118" s="11" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G118" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F118&amp;"|"&amp;$C118,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -19547,10 +19563,10 @@
         <v>35</v>
       </c>
       <c r="E119" s="11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F119" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G119" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F119&amp;"|"&amp;$C119,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -19599,10 +19615,10 @@
         <v>35</v>
       </c>
       <c r="E120" s="11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F120" s="11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G120" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F120&amp;"|"&amp;$C120,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -19651,10 +19667,10 @@
         <v>35</v>
       </c>
       <c r="E121" s="11" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F121" s="11" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G121" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F121&amp;"|"&amp;$C121,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -19706,7 +19722,7 @@
         <v>39</v>
       </c>
       <c r="F122" s="11" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G122" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F122&amp;"|"&amp;$C122,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -19755,10 +19771,10 @@
         <v>38</v>
       </c>
       <c r="E123" s="11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F123" s="11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G123" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F123&amp;"|"&amp;$C123,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -19807,10 +19823,10 @@
         <v>38</v>
       </c>
       <c r="E124" s="11" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F124" s="11" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G124" s="33" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F124&amp;"|"&amp;$C124,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -19847,7 +19863,7 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B125" s="38" t="s">
         <v>21</v>
@@ -19859,10 +19875,10 @@
         <v>32</v>
       </c>
       <c r="E125" s="38" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F125" s="38" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G125" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F125&amp;"|"&amp;$C125,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -19899,7 +19915,7 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B126" s="38" t="s">
         <v>21</v>
@@ -19911,10 +19927,10 @@
         <v>32</v>
       </c>
       <c r="E126" s="38" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F126" s="38" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G126" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F126&amp;"|"&amp;$C126,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -19951,7 +19967,7 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B127" s="38" t="s">
         <v>21</v>
@@ -19963,10 +19979,10 @@
         <v>32</v>
       </c>
       <c r="E127" s="38" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F127" s="38" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G127" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F127&amp;"|"&amp;$C127,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -20003,7 +20019,7 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B128" s="38" t="s">
         <v>21</v>
@@ -20015,10 +20031,10 @@
         <v>32</v>
       </c>
       <c r="E128" s="38" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F128" s="38" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G128" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F128&amp;"|"&amp;$C128,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -20055,7 +20071,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B129" s="38" t="s">
         <v>21</v>
@@ -20067,10 +20083,10 @@
         <v>32</v>
       </c>
       <c r="E129" s="38" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F129" s="38" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G129" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F129&amp;"|"&amp;$C129,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -20107,7 +20123,7 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B130" s="38" t="s">
         <v>21</v>
@@ -20119,10 +20135,10 @@
         <v>32</v>
       </c>
       <c r="E130" s="38" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F130" s="38" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G130" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F130&amp;"|"&amp;$C130,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -20159,7 +20175,7 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B131" s="38" t="s">
         <v>21</v>
@@ -20171,10 +20187,10 @@
         <v>32</v>
       </c>
       <c r="E131" s="38" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F131" s="38" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G131" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F131&amp;"|"&amp;$C131,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -20211,7 +20227,7 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B132" s="38" t="s">
         <v>21</v>
@@ -20223,10 +20239,10 @@
         <v>32</v>
       </c>
       <c r="E132" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F132" s="38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G132" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F132&amp;"|"&amp;$C132,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -20263,7 +20279,7 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B133" s="38" t="s">
         <v>21</v>
@@ -20275,10 +20291,10 @@
         <v>32</v>
       </c>
       <c r="E133" s="38" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F133" s="38" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G133" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F133&amp;"|"&amp;$C133,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -20315,7 +20331,7 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B134" s="38" t="s">
         <v>21</v>
@@ -20327,10 +20343,10 @@
         <v>32</v>
       </c>
       <c r="E134" s="38" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F134" s="38" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G134" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F134&amp;"|"&amp;$C134,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -20367,7 +20383,7 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B135" s="38" t="s">
         <v>21</v>
@@ -20382,7 +20398,7 @@
         <v>33</v>
       </c>
       <c r="F135" s="38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G135" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F135&amp;"|"&amp;$C135,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -20419,7 +20435,7 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B136" s="38" t="s">
         <v>21</v>
@@ -20434,7 +20450,7 @@
         <v>36</v>
       </c>
       <c r="F136" s="38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G136" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F136&amp;"|"&amp;$C136,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -20471,7 +20487,7 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B137" s="38" t="s">
         <v>21</v>
@@ -20483,10 +20499,10 @@
         <v>35</v>
       </c>
       <c r="E137" s="38" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F137" s="38" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G137" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F137&amp;"|"&amp;$C137,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -20523,7 +20539,7 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B138" s="38" t="s">
         <v>21</v>
@@ -20535,10 +20551,10 @@
         <v>35</v>
       </c>
       <c r="E138" s="38" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F138" s="38" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G138" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F138&amp;"|"&amp;$C138,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -20575,7 +20591,7 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B139" s="38" t="s">
         <v>21</v>
@@ -20587,10 +20603,10 @@
         <v>35</v>
       </c>
       <c r="E139" s="38" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F139" s="38" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G139" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F139&amp;"|"&amp;$C139,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -20627,7 +20643,7 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B140" s="38" t="s">
         <v>21</v>
@@ -20639,10 +20655,10 @@
         <v>35</v>
       </c>
       <c r="E140" s="38" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F140" s="38" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G140" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F140&amp;"|"&amp;$C140,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -20679,7 +20695,7 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B141" s="38" t="s">
         <v>21</v>
@@ -20691,10 +20707,10 @@
         <v>35</v>
       </c>
       <c r="E141" s="38" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F141" s="38" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G141" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F141&amp;"|"&amp;$C141,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -20731,7 +20747,7 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B142" s="38" t="s">
         <v>21</v>
@@ -20743,10 +20759,10 @@
         <v>35</v>
       </c>
       <c r="E142" s="38" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F142" s="38" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G142" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F142&amp;"|"&amp;$C142,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -20783,7 +20799,7 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B143" s="38" t="s">
         <v>21</v>
@@ -20795,10 +20811,10 @@
         <v>35</v>
       </c>
       <c r="E143" s="38" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F143" s="38" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G143" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F143&amp;"|"&amp;$C143,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -20835,7 +20851,7 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B144" s="38" t="s">
         <v>21</v>
@@ -20847,10 +20863,10 @@
         <v>35</v>
       </c>
       <c r="E144" s="38" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F144" s="38" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G144" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F144&amp;"|"&amp;$C144,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -20887,7 +20903,7 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B145" s="38" t="s">
         <v>21</v>
@@ -20899,10 +20915,10 @@
         <v>35</v>
       </c>
       <c r="E145" s="38" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F145" s="38" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G145" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F145&amp;"|"&amp;$C145,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -20939,7 +20955,7 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B146" s="38" t="s">
         <v>21</v>
@@ -20951,10 +20967,10 @@
         <v>35</v>
       </c>
       <c r="E146" s="38" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F146" s="38" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G146" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F146&amp;"|"&amp;$C146,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -20991,7 +21007,7 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B147" s="38" t="s">
         <v>21</v>
@@ -21003,10 +21019,10 @@
         <v>35</v>
       </c>
       <c r="E147" s="38" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F147" s="38" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G147" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F147&amp;"|"&amp;$C147,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -21043,7 +21059,7 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B148" s="38" t="s">
         <v>21</v>
@@ -21055,10 +21071,10 @@
         <v>35</v>
       </c>
       <c r="E148" s="38" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F148" s="38" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G148" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F148&amp;"|"&amp;$C148,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -21095,7 +21111,7 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B149" s="38" t="s">
         <v>21</v>
@@ -21107,10 +21123,10 @@
         <v>35</v>
       </c>
       <c r="E149" s="38" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F149" s="38" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G149" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F149&amp;"|"&amp;$C149,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -21147,7 +21163,7 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B150" s="38" t="s">
         <v>21</v>
@@ -21159,10 +21175,10 @@
         <v>35</v>
       </c>
       <c r="E150" s="38" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F150" s="38" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G150" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F150&amp;"|"&amp;$C150,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -21199,7 +21215,7 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B151" s="38" t="s">
         <v>21</v>
@@ -21211,10 +21227,10 @@
         <v>35</v>
       </c>
       <c r="E151" s="38" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F151" s="38" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G151" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F151&amp;"|"&amp;$C151,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -21251,7 +21267,7 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B152" s="38" t="s">
         <v>21</v>
@@ -21266,7 +21282,7 @@
         <v>39</v>
       </c>
       <c r="F152" s="38" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G152" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F152&amp;"|"&amp;$C152,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -21303,7 +21319,7 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B153" s="38" t="s">
         <v>21</v>
@@ -21315,10 +21331,10 @@
         <v>38</v>
       </c>
       <c r="E153" s="38" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F153" s="38" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G153" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F153&amp;"|"&amp;$C153,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -21355,7 +21371,7 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="38" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B154" s="38" t="s">
         <v>21</v>
@@ -21367,10 +21383,10 @@
         <v>38</v>
       </c>
       <c r="E154" s="38" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F154" s="38" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G154" s="39" t="str">
         <f aca="false">INDEX('Cost by Tier'!$F$5:$F$124,MATCH($F154&amp;"|"&amp;$C154,'Cost by Tier'!$R$5:$R$124,0))</f>
@@ -21407,7 +21423,7 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
